--- a/scenarios/03_raj_mission_planner/3.2_weather_sensitivity/outputs/weather_sensitivity_results.xlsx
+++ b/scenarios/03_raj_mission_planner/3.2_weather_sensitivity/outputs/weather_sensitivity_results.xlsx
@@ -499,10 +499,10 @@
         <v>241571</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>331.45</v>
+        <v>362.98</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4.46</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="5">
@@ -516,10 +516,10 @@
         <v>242522</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>332.46</v>
+        <v>364.03</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4.46</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="6">
@@ -533,10 +533,10 @@
         <v>243342</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>333.33</v>
+        <v>364.93</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.46</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         <v>244047</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>334.09</v>
+        <v>365.71</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.46</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="8">
@@ -567,10 +567,10 @@
         <v>244653</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>334.73</v>
+        <v>366.37</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.46</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="9">
@@ -584,10 +584,10 @@
         <v>245173</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>335.29</v>
+        <v>366.95</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.46</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="10">
@@ -601,10 +601,10 @@
         <v>245618</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>335.76</v>
+        <v>367.44</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="11">
@@ -618,10 +618,10 @@
         <v>245999</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>336.17</v>
+        <v>367.86</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="12">
@@ -635,10 +635,10 @@
         <v>246324</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>336.52</v>
+        <v>368.22</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="13">
@@ -652,10 +652,10 @@
         <v>246601</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>336.81</v>
+        <v>368.52</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="14">
@@ -669,10 +669,10 @@
         <v>246838</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>337.06</v>
+        <v>368.78</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="15">
@@ -686,10 +686,10 @@
         <v>247040</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>337.28</v>
+        <v>369.01</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="16">
@@ -703,10 +703,10 @@
         <v>247212</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>337.46</v>
+        <v>369.2</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="17">
@@ -720,10 +720,10 @@
         <v>247358</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>337.62</v>
+        <v>369.36</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="18">
@@ -737,10 +737,10 @@
         <v>247483</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>337.75</v>
+        <v>369.5</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="19">
@@ -754,10 +754,10 @@
         <v>247589</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>337.87</v>
+        <v>369.62</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="20">
@@ -771,10 +771,10 @@
         <v>247680</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>337.96</v>
+        <v>369.72</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="21">
@@ -788,10 +788,10 @@
         <v>247756</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>338.05</v>
+        <v>369.8</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="22">
@@ -805,10 +805,10 @@
         <v>247822</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>338.12</v>
+        <v>369.87</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="23">
@@ -822,10 +822,10 @@
         <v>247877</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>338.18</v>
+        <v>369.93</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="24">
@@ -839,10 +839,10 @@
         <v>247925</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>338.23</v>
+        <v>369.99</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="25">
@@ -856,10 +856,10 @@
         <v>247965</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>338.27</v>
+        <v>370.03</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="26">
@@ -873,10 +873,10 @@
         <v>247999</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>338.31</v>
+        <v>370.07</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="27">
@@ -890,10 +890,10 @@
         <v>248028</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>338.34</v>
+        <v>370.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="28">
@@ -907,10 +907,10 @@
         <v>248053</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>338.36</v>
+        <v>370.13</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>4.47</v>
+        <v>4.3</v>
       </c>
     </row>
   </sheetData>
@@ -979,10 +979,10 @@
         <v>287663</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>374.1</v>
+        <v>405.6</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="5">
@@ -996,10 +996,10 @@
         <v>270811</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>359.26</v>
+        <v>390.91</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4.51</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         <v>256923</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>346.61</v>
+        <v>378.34</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.49</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="7">
@@ -1030,10 +1030,10 @@
         <v>245470</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>335.85</v>
+        <v>367.6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="8">
@@ -1047,10 +1047,10 @@
         <v>236019</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>326.74</v>
+        <v>358.47</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>4.45</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="9">
@@ -1064,10 +1064,10 @@
         <v>228215</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>319.03</v>
+        <v>350.72</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>4.43</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="10">
@@ -1081,10 +1081,10 @@
         <v>221767</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>312.52</v>
+        <v>344.15</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>4.42</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="11">
@@ -1098,10 +1098,10 @@
         <v>216437</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>307.04</v>
+        <v>338.59</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4.4</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="12">
@@ -1115,10 +1115,10 @@
         <v>212027</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>302.43</v>
+        <v>333.9</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>4.39</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="13">
@@ -1132,10 +1132,10 @@
         <v>208376</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>298.55</v>
+        <v>329.94</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>4.39</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="14">
@@ -1149,10 +1149,10 @@
         <v>205353</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>295.29</v>
+        <v>326.6</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>4.38</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="15">
@@ -1166,10 +1166,10 @@
         <v>202847</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>292.55</v>
+        <v>323.79</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="16">
@@ -1183,10 +1183,10 @@
         <v>200769</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>290.25</v>
+        <v>321.42</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="17">
@@ -1200,10 +1200,10 @@
         <v>199045</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>288.32</v>
+        <v>319.42</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4.36</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="18">
@@ -1217,10 +1217,10 @@
         <v>197614</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>286.69</v>
+        <v>317.73</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>4.36</v>
+        <v>4.19</v>
       </c>
     </row>
   </sheetData>
@@ -1297,10 +1297,10 @@
         <v>0.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>360.85</v>
+        <v>392.51</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4.51</v>
+        <v>4.33</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>352.41</v>
+        <v>384.12</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1345,10 +1345,10 @@
         <v>1.4</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>337.87</v>
+        <v>369.61</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>320.85</v>
+        <v>352.52</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.43</v>
+        <v>4.26</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>302.4</v>
+        <v>333.83</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.39</v>
+        <v>4.23</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>291.21</v>
+        <v>322.33</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>286.57</v>
+        <v>317.6</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4.36</v>
+        <v>4.19</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
         <v>0.5</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>374.64</v>
+        <v>406.15</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1548,22 +1548,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>4.52</v>
+        <v>4.34</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>4.48</v>
+        <v>4.3</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4.46</v>
+        <v>4.28</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>4.39</v>
+        <v>4.22</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>4.36</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="5">
@@ -1571,22 +1571,22 @@
         <v>5</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>4.53</v>
+        <v>4.35</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>4.49</v>
+        <v>4.31</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4.46</v>
+        <v>4.29</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>4.43</v>
+        <v>4.26</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>4.39</v>
+        <v>4.23</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4.36</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="6">
@@ -1594,22 +1594,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>4.54</v>
+        <v>4.35</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>4.43</v>
+        <v>4.26</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>4.4</v>
+        <v>4.23</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>4.36</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="7">
@@ -1617,22 +1617,22 @@
         <v>23</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>4.44</v>
+        <v>4.26</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4.4</v>
+        <v>4.23</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>4.36</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="8">
@@ -1640,22 +1640,22 @@
         <v>50</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>4.44</v>
+        <v>4.26</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>4.4</v>
+        <v>4.23</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>4.36</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="9">
@@ -1663,22 +1663,22 @@
         <v>100</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4.47</v>
+        <v>4.3</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4.44</v>
+        <v>4.26</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4.4</v>
+        <v>4.23</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>4.36</v>
+        <v>4.19</v>
       </c>
     </row>
   </sheetData>
